--- a/docs/downloads/经营分_津河省区__津南片区_2026-10-19.xlsx
+++ b/docs/downloads/经营分_津河省区__津南片区_2026-10-19.xlsx
@@ -12,7 +12,7 @@
     <sheet name="匹配异常" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'匹配异常'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -768,40 +768,36 @@
           <t>津南片区</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>6888584502277326861</t>
+          <t>7560634595620685833</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IU酒店（天津津南国家会展中心大学城店）</t>
+          <t>7天优品Premium酒店(天津五大道佟楼地铁站店)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>iu酒店(天津津南国家会展中心大学城店)</t>
+          <t>7天优品Premium酒店(天津五大道佟楼地铁站店)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -817,19 +813,19 @@
         <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P3" t="n">
         <v>30</v>
       </c>
       <c r="Q3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
         <v>30</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>20</v>
@@ -863,29 +859,29 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>7081317759820236811</t>
+          <t>6888584502277326861</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津国家会展中心津南大学城店)</t>
+          <t>IU酒店（天津津南国家会展中心大学城店）</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津国家会展中心津南大学城店)</t>
+          <t>iu酒店(天津津南国家会展中心大学城店)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>70</v>
       </c>
       <c r="I4" t="n">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -899,7 +895,7 @@
         <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>30</v>
@@ -911,7 +907,7 @@
         <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R4" t="n">
         <v>30</v>
@@ -944,20 +940,24 @@
           <t>津南片区</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>6601155474995808270</t>
+          <t>7081317759820236811</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店天津北闸口镇店</t>
+          <t>维也纳酒店(天津国家会展中心津南大学城店)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>希岸酒店(天津北闸口镇店)</t>
+          <t>维也纳酒店(天津国家会展中心津南大学城店)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I5" t="n">
         <v>-10</v>
@@ -983,7 +983,7 @@
         <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
         <v>30</v>
@@ -995,7 +995,7 @@
         <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
         <v>30</v>
@@ -1028,24 +1028,20 @@
           <t>津南片区</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>6678148308814268419</t>
+          <t>6601155474995808270</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>维也纳酒店（五大道友谊路文化中心地铁站店）</t>
+          <t>希岸·轻雅酒店天津北闸口镇店</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津友谊路五大道店)</t>
+          <t>希岸酒店(天津北闸口镇店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1057,7 +1053,7 @@
         <v>72</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1116,32 +1112,36 @@
           <t>津南片区</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>6732804669405497351</t>
+          <t>6678148308814268419</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（天津机场店）</t>
+          <t>维也纳酒店（五大道友谊路文化中心地铁站店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(天津机场店)</t>
+          <t>维也纳酒店(天津友谊路五大道店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I7" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N7" t="n">
         <v>30</v>
@@ -1200,24 +1200,20 @@
           <t>津南片区</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7028040302908672000</t>
+          <t>6732804669405497351</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>麗枫酒店天津梅江会展复兴门地铁站店</t>
+          <t>维也纳国际酒店（天津机场店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津梅江会展复兴门地铁站店)</t>
+          <t>维也纳国际酒店(天津机场店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1226,24 +1222,24 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
@@ -1255,7 +1251,7 @@
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1295,17 +1291,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7373180892628158505</t>
+          <t>7028040302908672000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7天酒店·天津津南北闸口镇店</t>
+          <t>麗枫酒店天津梅江会展复兴门地铁站店</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7天酒店(天津津南北闸口镇店)</t>
+          <t>麗枫酒店(天津梅江会展复兴门地铁站店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1314,24 +1310,24 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
@@ -1383,29 +1379,29 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6601138347408623630</t>
+          <t>7373180892628158505</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>派酒店（天津宾馆地铁站市政府店）</t>
+          <t>7天酒店·天津津南北闸口镇店</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>派酒店(天津宾馆地铁站市政府店)</t>
+          <t>7天酒店(天津津南北闸口镇店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>85</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1471,17 +1467,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6601131530519578632</t>
+          <t>6601138347408623630</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7天酒店（天津奥体中心肿瘤医院地铁站）</t>
+          <t>派酒店（天津宾馆地铁站市政府店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7天酒店(天津肿瘤医院地铁站店)</t>
+          <t>派酒店(天津宾馆地铁站市政府店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1490,10 +1486,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1507,7 +1503,7 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
@@ -1519,7 +1515,7 @@
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1559,29 +1555,29 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7371773508466804772</t>
+          <t>6601131530519578632</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>希岸酒店天津奥体中心肿瘤医院地铁站店</t>
+          <t>7天酒店（天津奥体中心肿瘤医院地铁站）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>希岸酒店(天津奥体中心肿瘤医院地铁站店)</t>
+          <t>7天酒店(天津肿瘤医院地铁站店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>87</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1595,7 +1591,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
@@ -1607,7 +1603,7 @@
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
@@ -1647,17 +1643,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7045846491030390819</t>
+          <t>7371773508466804772</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（天津国展吾悦广场店）</t>
+          <t>希岸酒店天津奥体中心肿瘤医院地铁站店</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(天津国展吾悦广场店)</t>
+          <t>希岸酒店(天津奥体中心肿瘤医院地铁站店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1735,17 +1731,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7301176193271728137</t>
+          <t>7045846491030390819</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津国家会展中心星光大道店)</t>
+          <t>维也纳国际酒店（天津国展吾悦广场店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津国家会展中心星光大道店)</t>
+          <t>维也纳国际酒店(天津国展吾悦广场店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1777,13 +1773,13 @@
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1823,17 +1819,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7254426995033901111</t>
+          <t>7301176193271728137</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津小白楼地铁站店</t>
+          <t>维也纳酒店(天津国家会展中心星光大道店)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津小白楼地铁站店)</t>
+          <t>维也纳酒店(天津国家会展中心星光大道店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1865,13 +1861,13 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1911,17 +1907,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>7234811941300996157</t>
+          <t>7254426995033901111</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津国家会展中心津南大学城店</t>
+          <t>麗枫酒店·天津小白楼地铁站店</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>麗枫酒店(津南国家会展中心大学城店)</t>
+          <t>麗枫酒店(天津小白楼地铁站店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1930,18 +1926,18 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
         <v>10</v>
@@ -1959,7 +1955,7 @@
         <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R16" t="n">
         <v>30</v>
@@ -1999,17 +1995,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6702211947191896077</t>
+          <t>7234811941300996157</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津五大道友谊路文化中心地铁站店）</t>
+          <t>麗枫酒店·天津国家会展中心津南大学城店</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津五大道友谊路文化中心地铁站店)</t>
+          <t>麗枫酒店(津南国家会展中心大学城店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2018,18 +2014,18 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
         <v>10</v>
@@ -2041,13 +2037,13 @@
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2087,17 +2083,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7315682465337739276</t>
+          <t>6702211947191896077</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津奥体中心肿瘤医院地铁站店）</t>
+          <t>喆啡酒店（天津五大道友谊路文化中心地铁站店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津奥体中心肿瘤医院店)</t>
+          <t>喆啡酒店(天津五大道友谊路文化中心地铁站店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2109,7 +2105,7 @@
         <v>92</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2129,13 +2125,13 @@
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2175,17 +2171,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7088949461086390303</t>
+          <t>7315682465337739276</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>麗枫酒店（天津站五大道景区店）</t>
+          <t>喆啡酒店（天津奥体中心肿瘤医院地铁站店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津站五大道景区店)</t>
+          <t>喆啡酒店(天津奥体中心肿瘤医院店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2211,13 +2207,13 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
@@ -2263,17 +2259,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7066985349183965225</t>
+          <t>7088949461086390303</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津津南领世郡双港地铁站店）</t>
+          <t>麗枫酒店（天津站五大道景区店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津津南领世郡双港地铁站店)</t>
+          <t>麗枫酒店(天津站五大道景区店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2282,24 +2278,24 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2351,17 +2347,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>6601137735086376973</t>
+          <t>7066985349183965225</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IU酒店 天津五大道吴家窑地铁站店</t>
+          <t>维也纳酒店（天津津南领世郡双港地铁站店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>iu酒店(天津天塔景区吴家窑地铁站店)</t>
+          <t>维也纳酒店(天津津南领世郡双港地铁站店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2370,30 +2366,30 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
         <v>10</v>
       </c>
       <c r="M21" t="n">
+        <v>22</v>
+      </c>
+      <c r="N21" t="n">
+        <v>30</v>
+      </c>
+      <c r="O21" t="n">
         <v>25</v>
-      </c>
-      <c r="N21" t="n">
-        <v>30</v>
-      </c>
-      <c r="O21" t="n">
-        <v>20</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
@@ -2439,17 +2435,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7524979893952579599</t>
+          <t>6601137735086376973</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>天津梅江会展中心锦江都城酒店</t>
+          <t>IU酒店 天津五大道吴家窑地铁站店</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>天津梅江会展中心锦江都城酒店</t>
+          <t>iu酒店(天津天塔景区吴家窑地铁站店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2458,14 +2454,14 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2475,19 +2471,19 @@
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
         <v>30</v>
@@ -2527,29 +2523,29 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6979341143678912543</t>
+          <t>7524979893952579599</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（天津国展小站米立方店）</t>
+          <t>天津梅江会展中心锦江都城酒店</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(天津国展小站米立方店)</t>
+          <t>天津梅江会展中心锦江都城酒店</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>97</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2615,33 +2611,33 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7600620871023069219</t>
+          <t>6979341143678912543</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>锦江之星（5.0天津梅江会展医大二院地铁站店）</t>
+          <t>维也纳国际酒店（天津国展小站米立方店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>锦江之星酒店(天津医大二院地铁站店)</t>
+          <t>维也纳国际酒店(天津国展小站米立方店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2651,19 +2647,19 @@
         <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N24" t="n">
         <v>30</v>
       </c>
       <c r="O24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P24" t="n">
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2703,37 +2699,37 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7231891677697280058</t>
+          <t>7600620871023069219</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7天酒店（天津咸水沽国家会展中心店）</t>
+          <t>锦江之星（5.0天津梅江会展医大二院地铁站店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7天酒店(天津咸水沽国家会展中心店)</t>
+          <t>锦江之星酒店(天津医大二院地铁站店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
         <v>10</v>
@@ -2745,7 +2741,7 @@
         <v>30</v>
       </c>
       <c r="O25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P25" t="n">
         <v>30</v>
@@ -2791,43 +2787,43 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>6924792443753728000</t>
+          <t>7231891677697280058</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0天津陈塘庄地铁站店)</t>
+          <t>7天酒店（天津咸水沽国家会展中心店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0天津陈塘庄地铁站店)</t>
+          <t>7天酒店(天津咸水沽国家会展中心店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>搭门店,稳房源,拿收益</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
@@ -2879,17 +2875,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>6601141215712790541</t>
+          <t>6924792443753728000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>丽怡酒店天津梅江会展中心医科大学第二医院店</t>
+          <t>维也纳酒店（5.0天津陈塘庄地铁站店)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>丽怡酒店(天津文化中心医大二院地铁站店)</t>
+          <t>维也纳酒店(5.0天津陈塘庄地铁站店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2898,14 +2894,14 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2915,7 +2911,7 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
@@ -2967,17 +2963,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7001683011994159141</t>
+          <t>6601141215712790541</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（天津国家会展中心职业技术师范大学店）</t>
+          <t>丽怡酒店天津梅江会展中心医科大学第二医院店</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(天津国家会展中心职业技术师范大学店)</t>
+          <t>丽怡酒店(天津文化中心医大二院地铁站店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2989,7 +2985,7 @@
         <v>110</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -3055,17 +3051,17 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>6601141169252468743</t>
+          <t>7001683011994159141</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>锦江之星品尚（天津五大道小白楼地铁站酒店）</t>
+          <t>维也纳国际酒店（天津国家会展中心职业技术师范大学店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>锦江之星品尚酒店(天津五大道小白楼地铁站店)</t>
+          <t>维也纳国际酒店(天津国家会展中心职业技术师范大学店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3081,7 +3077,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>稳房源,提质量</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3091,19 +3087,19 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
@@ -3143,17 +3139,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7606579912758593588</t>
+          <t>6601141169252468743</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>麗枫酒店（天津奥体中心天塔湖景区店）</t>
+          <t>锦江之星品尚（天津五大道小白楼地铁站酒店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津奥体中心天塔湖景区店)</t>
+          <t>锦江之星品尚酒店(天津五大道小白楼地铁站店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3165,11 +3161,11 @@
         <v>110</v>
       </c>
       <c r="I30" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,提质量</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3179,19 +3175,19 @@
         <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N30" t="n">
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3231,79 +3227,167 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
+          <t>7606579912758593588</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>麗枫酒店（天津奥体中心天塔湖景区店）</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>麗枫酒店(天津奥体中心天塔湖景区店)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>已认证</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>110</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>拿收益</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" t="n">
+        <v>10</v>
+      </c>
+      <c r="M31" t="n">
+        <v>30</v>
+      </c>
+      <c r="N31" t="n">
+        <v>30</v>
+      </c>
+      <c r="O31" t="n">
+        <v>30</v>
+      </c>
+      <c r="P31" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>20</v>
+      </c>
+      <c r="R31" t="n">
+        <v>30</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="n">
+        <v>20</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>7249997748999555075</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>汇通百达网络科技（上海）有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>津河省区</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>津南片区</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
           <t>7537947469422790708</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>喆啡酒店（天津五大道小白楼地铁站店）</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>喆啡酒店(天津五大道小白楼地铁站店)</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>已认证</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="H32" t="n">
         <v>120</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I32" t="n">
         <v>0</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>10</v>
-      </c>
-      <c r="L31" t="n">
-        <v>10</v>
-      </c>
-      <c r="M31" t="n">
-        <v>30</v>
-      </c>
-      <c r="N31" t="n">
-        <v>30</v>
-      </c>
-      <c r="O31" t="n">
-        <v>30</v>
-      </c>
-      <c r="P31" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>30</v>
-      </c>
-      <c r="R31" t="n">
-        <v>30</v>
-      </c>
-      <c r="S31" t="n">
-        <v>20</v>
-      </c>
-      <c r="T31" t="n">
-        <v>20</v>
-      </c>
-      <c r="U31" t="inlineStr">
+      <c r="K32" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10</v>
+      </c>
+      <c r="M32" t="n">
+        <v>30</v>
+      </c>
+      <c r="N32" t="n">
+        <v>30</v>
+      </c>
+      <c r="O32" t="n">
+        <v>30</v>
+      </c>
+      <c r="P32" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>30</v>
+      </c>
+      <c r="R32" t="n">
+        <v>30</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="n">
+        <v>20</v>
+      </c>
+      <c r="U32" t="inlineStr">
         <is>
           <t>7249997748999555075</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>汇通百达网络科技（上海）有限公司</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V31"/>
-  <conditionalFormatting sqref="H2:H31">
+  <autoFilter ref="A1:V32"/>
+  <conditionalFormatting sqref="H2:H32">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -3315,7 +3399,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I31">
+  <conditionalFormatting sqref="I2:I32">
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
